--- a/examples/output/edge-formulas.xlsx
+++ b/examples/output/edge-formulas.xlsx
@@ -80,6 +80,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins bottom="0.7500" footer="0.3000" header="0.3000" left="0.7000" right="0.7000" top="0.7500"/>
 </worksheet>
 </file>